--- a/Deterministic/Model Files/Segment Test/data/production_capacity_scenarios_NEW_20JUN.xlsx
+++ b/Deterministic/Model Files/Segment Test/data/production_capacity_scenarios_NEW_20JUN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/Model Files/L-Shaped/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uark-my.sharepoint.com/personal/uhorchak_uark_edu/Documents/Desktop/Vaccine_Tender/Deterministic/Model Files/Segment Test/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{6259234B-0F6C-41FA-846B-135095B5B389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B485FBE-000F-46BD-ADDD-C5D0F13F4293}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{6259234B-0F6C-41FA-846B-135095B5B389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{465C743C-49CC-4CB4-A6F3-37ECE1C682E4}"/>
   <bookViews>
-    <workbookView xWindow="-21710" yWindow="-15900" windowWidth="21820" windowHeight="37900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base_capacity" sheetId="1" r:id="rId1"/>
@@ -452,12 +452,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -492,7 +493,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -527,7 +528,7 @@
         <v>12100000</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -562,7 +563,7 @@
         <v>55800000</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -597,7 +598,7 @@
         <v>5460000</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -632,7 +633,7 @@
         <v>18900000</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -667,7 +668,7 @@
         <v>677000000</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -702,7 +703,7 @@
         <v>1320000</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -737,7 +738,7 @@
         <v>380000000</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -772,7 +773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -807,7 +808,7 @@
         <v>89200000</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -842,7 +843,7 @@
         <v>31900000</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -877,7 +878,7 @@
         <v>14000000</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -912,7 +913,7 @@
         <v>127000000</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -947,7 +948,7 @@
         <v>42800000</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -982,7 +983,7 @@
         <v>102000000</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1025,9 +1026,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1062,7 +1063,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1097,7 +1098,7 @@
         <v>7711003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1132,7 +1133,7 @@
         <v>39223956</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1167,7 +1168,7 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1202,7 +1203,7 @@
         <v>12048153</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1237,7 +1238,7 @@
         <v>164885690</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1272,7 +1273,7 @@
         <v>12812242</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1307,7 +1308,7 @@
         <v>226762686</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1342,7 +1343,7 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1377,7 +1378,7 @@
         <v>43702188</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1412,7 +1413,7 @@
         <v>56991052</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1447,7 +1448,7 @@
         <v>45911731</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1482,7 +1483,7 @@
         <v>10874165</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1517,7 +1518,7 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1552,7 +1553,7 @@
         <v>87429432</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1595,9 +1596,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1632,7 +1633,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1667,7 +1668,7 @@
         <v>7711003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1702,7 +1703,7 @@
         <v>39223956</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1737,7 +1738,7 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1772,7 +1773,7 @@
         <v>12048153</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1807,7 +1808,7 @@
         <v>164885690</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1842,7 +1843,7 @@
         <v>12812242</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1877,7 +1878,7 @@
         <v>226762686</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1912,7 +1913,7 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1947,7 +1948,7 @@
         <v>43702188</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1982,7 +1983,7 @@
         <v>56991052</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2017,7 +2018,7 @@
         <v>45911731</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2052,7 +2053,7 @@
         <v>10874165</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2087,7 +2088,7 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -2122,7 +2123,7 @@
         <v>87429432</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2165,9 +2166,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2202,7 +2203,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2237,7 +2238,7 @@
         <v>7711003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2272,7 +2273,7 @@
         <v>39223956</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2307,7 +2308,7 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2342,7 +2343,7 @@
         <v>12048153</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2377,7 +2378,7 @@
         <v>164885690</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -2412,7 +2413,7 @@
         <v>12812242</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2447,7 +2448,7 @@
         <v>226762686</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -2482,7 +2483,7 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2517,7 +2518,7 @@
         <v>43702188</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -2552,7 +2553,7 @@
         <v>56991052</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2587,7 +2588,7 @@
         <v>45911731</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2622,7 +2623,7 @@
         <v>10874165</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2657,7 +2658,7 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -2692,7 +2693,7 @@
         <v>87429432</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2735,9 +2736,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2772,7 +2773,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2807,7 +2808,7 @@
         <v>7711003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2842,7 +2843,7 @@
         <v>39223956</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2877,7 +2878,7 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2912,7 +2913,7 @@
         <v>12048153</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2947,7 +2948,7 @@
         <v>164885690</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -2982,7 +2983,7 @@
         <v>12812242</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -3017,7 +3018,7 @@
         <v>226762686</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -3052,7 +3053,7 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -3087,7 +3088,7 @@
         <v>43702188</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -3122,7 +3123,7 @@
         <v>56991052</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -3157,7 +3158,7 @@
         <v>45911731</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -3192,7 +3193,7 @@
         <v>10874165</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -3227,7 +3228,7 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -3262,7 +3263,7 @@
         <v>87429432</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -3305,9 +3306,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3342,7 +3343,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3377,7 +3378,7 @@
         <v>7711003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3412,7 +3413,7 @@
         <v>39223956</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3447,7 +3448,7 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3482,7 +3483,7 @@
         <v>12048153</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -3517,7 +3518,7 @@
         <v>164885690</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -3552,7 +3553,7 @@
         <v>12812242</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -3587,7 +3588,7 @@
         <v>226762686</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -3622,7 +3623,7 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -3657,7 +3658,7 @@
         <v>43702188</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -3692,7 +3693,7 @@
         <v>56991052</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -3727,7 +3728,7 @@
         <v>45911731</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -3762,7 +3763,7 @@
         <v>10874165</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -3797,7 +3798,7 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -3832,7 +3833,7 @@
         <v>87429432</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -3875,13 +3876,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3916,7 +3917,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3951,7 +3952,7 @@
         <v>7711003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3986,7 +3987,7 @@
         <v>39223956</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4021,7 +4022,7 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -4056,7 +4057,7 @@
         <v>12048153</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -4091,7 +4092,7 @@
         <v>164885690</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -4126,7 +4127,7 @@
         <v>12812242</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -4161,7 +4162,7 @@
         <v>226762686</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -4196,7 +4197,7 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -4231,7 +4232,7 @@
         <v>43702188</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -4266,7 +4267,7 @@
         <v>56991052</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -4301,7 +4302,7 @@
         <v>45911731</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -4336,7 +4337,7 @@
         <v>10874165</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -4371,7 +4372,7 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -4406,7 +4407,7 @@
         <v>87429432</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
